--- a/input/mapping/099. OCB_GOLD_TTDL_DIM_DEPOSIT_Huy.xlsx
+++ b/input/mapping/099. OCB_GOLD_TTDL_DIM_DEPOSIT_Huy.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\OCB\datavault-model\reverse\result\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DE6AEB-AE5A-4767-9FF3-08F6ACC86D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4E75431099DB82B0B092ABD1A36B838AA465B7AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1541C839-6ACA-4EEB-96EF-9600AB6212B8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,14 +242,14 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t>DIM_DEPOSIT (Gold VIEW)</t>
+    <t>DIM_DEPOSIT (Gold DML — SCD2 MERGE (giu lich su))</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tcimport;
-CREATE OR REPLACE VIEW DIM_DEPOSIT AS
+MERGE INTO tcimport.DIM_DEPOSIT tgt
+USING (
 WITH
--- Driver: hub_crb (TK tien gui) hieu luc
 crb_del AS (
     SELECT crb_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_crb')
     WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
@@ -267,10 +262,9 @@
     WHERE d.crb_hashkey IS NULL
       AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
       AND h.record_source = 't24__t24_crb'
-      AND LEFT(h.gl, 2) IN ('42','43','44')   -- KHOP IBM: GL tien gui (hub_crb phoi cot gl)
+      AND LEFT(h.gl, 2) IN ('42','43','44')
     GROUP BY h.crb_hashkey, h.tieukhoan
 ),
--- Bridge account (non-LD) / loans (LD) theo so TK
 acct_hub AS (
     SELECT business_key AS account_no, max_by(account_hashkey, source_event_date) AS account_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
@@ -314,7 +308,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
     GROUP BY loans_hashkey
 ),
--- Deposit AZ (hub_deposits) — dates chinh xac + INTEREST_BASIS (SUY LUAN THEM)
 dep_del AS (
     SELECT deposit_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_deposits')
     WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
@@ -351,7 +344,6 @@
     WHERE ref_type = 'az_product_parameter' AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
     GROUP BY ref_code
 ),
--- Khach hang (link_crb_customer)
 crb_cust AS (
     SELECT crb_hashkey, max_by(customer_hashkey, source_event_date) AS customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_customer')
@@ -371,7 +363,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd') AND h.record_source = 't24__t24_customer'
     GROUP BY h.customer_hashkey, h.business_key
 ),
--- Chi nhanh (link_crb_branch) -- SUY LUAN THEM (mapping de NULL)
 crb_branch AS (
     SELECT crb_hashkey, max_by(branch_hashkey, source_event_date) AS branch_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_branch')
@@ -391,7 +382,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd') AND h.record_source = 't24__t24_company'
     GROUP BY h.branch_hashkey, h.business_key
 ),
--- Can bo (account officer + LD middleman) -&gt; hub_acct_officer dung lai 2 vai tro
 acct_off_lnk AS (
     SELECT account_hashkey, max_by(dept_acct_officer_hashkey, source_event_date) AS dept_acct_officer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_dept_acct_officer')
@@ -410,7 +400,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
     GROUP BY dept_acct_officer_hashkey
 ),
--- TK bi phong toa: account co locked event (loai da xoa)
 locked_del AS (
     SELECT ac_locked_events_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_account_locked_events')
     WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
@@ -428,35 +417,34 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_category')
     WHERE ref_type = 'category' AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
     GROUP BY ref_code
-)
+),
+base AS (
 SELECT
-    c.crb_hashkey                               AS DIMENSION_KEY,       -- surrogate on dinh DV (dsx = SCD2 SEQ)
-    CAST(NULL AS DATE)                          AS EFF_FROM_DATE,
-    CAST(NULL AS DATE)                          AS EFF_TO_DATE,
-    CAST(CASE WHEN c.account_no LIKE 'LD%' THEN REPLACE(mid.officer_code,'ACOFFICER','') ELSE NULL END AS STRING) AS AC_MIDDLEMAN_LD,  -- TODO(DA) non-LD = T_REF_OFFICER
+    c.crb_hashkey                               AS DIMENSION_KEY,
+    CAST(CASE WHEN c.account_no LIKE 'LD%' THEN REPLACE(mid.officer_code,'ACOFFICER','') ELSE NULL END AS STRING) AS AC_MIDDLEMAN_LD,
     CAST(CASE WHEN c.account_no LIKE 'LD%' THEN lcl.t_category ELSE COALESCE(dcl.t_category, acl.t_category) END AS STRING) AS DEPO_PROD_CODE,
     CAST(rc.product_name AS STRING)             AS DEPO_PROD_NAME,
-    COALESCE(di.t_value_date, ai.t_opening_date) AS START_DATE,         -- AZ deposit value_date uu tien
+    COALESCE(di.t_value_date, ai.t_opening_date) AS START_DATE,
     CAST(c.account_no AS STRING)                AS ACCOUNT_NO,
-    CAST(bd.branch_code AS STRING)              AS BRANCH_CODE,         -- SUY LUAN THEM: link_crb_branch
+    CAST(bd.branch_code AS STRING)              AS BRANCH_CODE,
     CAST(cu.customer_id AS STRING)              AS CUSTOMER_ID,
     COALESCE(di.t_rollover_date, ai.t_create_date) AS ROLLOVER_DATE,
     COALESCE(di.t_maturity_date, ai.t_mature_date) AS MATURITY_DATE,
     CAST(REPLACE(aof.officer_code,'ACOFFICER','') AS STRING) AS ACCOUNT_OFFICER_ID,
-    CAST(NULL AS STRING)                        AS FTP_TYPE_BOND,       -- IBM hard NULL
-    CAST(NULL AS STRING)                        AS ACCOUNT_STATUS,      -- IBM hard NULL
-    CAST(NULL AS STRING)                        AS FTP_RIGHT,           -- IBM hard NULL
-    CAST(NULL AS DATE)                          AS NEXT_RIGHTS_DATE,    -- IBM hard NULL
-    CAST(NULL AS STRING)                        AS FTP_TERM_RIGHT,      -- IBM hard NULL
-    CAST(NULL AS STRING)                        AS INTEREST_TYPE,       -- IBM hard NULL
-    CAST(NULL AS STRING)                        AS MATURITY_TREATMENT,  -- IBM hard NULL
+    CAST(NULL AS STRING)                        AS FTP_TYPE_BOND,
+    CAST(NULL AS STRING)                        AS ACCOUNT_STATUS,
+    CAST(NULL AS STRING)                        AS FTP_RIGHT,
+    CAST(NULL AS DATE)                          AS NEXT_RIGHTS_DATE,
+    CAST(NULL AS STRING)                        AS FTP_TERM_RIGHT,
+    CAST(NULL AS STRING)                        AS INTEREST_TYPE,
+    CAST(NULL AS STRING)                        AS MATURITY_TREATMENT,
     CAST(CASE WHEN c.account_no LIKE 'LD%' THEN lcl.t_ld_cust_group ELSE acl.t_cust_group END AS STRING) AS CUSTGROUP_AR,
-    CAST(raz.t_int_basis AS STRING)             AS INTEREST_BASIS,      -- SUY LUAN THEM: ref_t24_az_product_parameter qua t_all_in_one_product
+    CAST(raz.t_int_basis AS STRING)             AS INTEREST_BASIS,
     CURRENT_TIMESTAMP                           AS CRT_TM,
     CURRENT_TIMESTAMP                           AS PPN_TM,
-    CAST(c.account_no AS STRING)                AS AR_ID,               -- KHOP mapping = hub_crb.business_key
+    CAST(c.account_no AS STRING)                AS AR_ID,
     CAST(ELEMENT_AT(SPLIT(asys.t_inputter,'_'),2) AS STRING) AS USER_CREATED,
-    'N'                                         AS IS_HDTG_DANANG,      -- TODO(DA): IBM tu AC_X_USR_CRT, DV chua co quan he
+    'N'                                         AS IS_HDTG_DANANG,
     CASE WHEN lk.account_hashkey IS NOT NULL THEN 'Y' ELSE 'N' END AS BLOCKED_ACCOUNT
 FROM crb_active c
 LEFT JOIN acct_hub  ah  ON ah.account_no = c.account_no
@@ -479,7 +467,129 @@
 LEFT JOIN loans_mid_lnk lml ON lml.loans_hashkey = lh.loans_hashkey
 LEFT JOIN officer_hub  mid ON mid.dept_acct_officer_hashkey = lml.dept_acct_officer_hashkey
 LEFT JOIN locked_acct  lk  ON lk.account_hashkey = ah.account_hashkey
-;
+)
+SELECT base.DIMENSION_KEY AS mergeKey,
+        base.AC_MIDDLEMAN_LD,
+        base.DEPO_PROD_CODE,
+        base.DEPO_PROD_NAME,
+        base.START_DATE,
+        base.ACCOUNT_NO,
+        base.BRANCH_CODE,
+        base.CUSTOMER_ID,
+        base.ROLLOVER_DATE,
+        base.MATURITY_DATE,
+        base.ACCOUNT_OFFICER_ID,
+        base.FTP_TYPE_BOND,
+        base.ACCOUNT_STATUS,
+        base.FTP_RIGHT,
+        base.NEXT_RIGHTS_DATE,
+        base.FTP_TERM_RIGHT,
+        base.INTEREST_TYPE,
+        base.MATURITY_TREATMENT,
+        base.CUSTGROUP_AR,
+        base.INTEREST_BASIS,
+        base.CRT_TM,
+        base.PPN_TM,
+        base.AR_ID,
+        base.USER_CREATED,
+        base.IS_HDTG_DANANG,
+        base.BLOCKED_ACCOUNT
+FROM base
+UNION ALL
+SELECT CAST(NULL AS STRING) AS mergeKey,
+        base.AC_MIDDLEMAN_LD,
+        base.DEPO_PROD_CODE,
+        base.DEPO_PROD_NAME,
+        base.START_DATE,
+        base.ACCOUNT_NO,
+        base.BRANCH_CODE,
+        base.CUSTOMER_ID,
+        base.ROLLOVER_DATE,
+        base.MATURITY_DATE,
+        base.ACCOUNT_OFFICER_ID,
+        base.FTP_TYPE_BOND,
+        base.ACCOUNT_STATUS,
+        base.FTP_RIGHT,
+        base.NEXT_RIGHTS_DATE,
+        base.FTP_TERM_RIGHT,
+        base.INTEREST_TYPE,
+        base.MATURITY_TREATMENT,
+        base.CUSTGROUP_AR,
+        base.INTEREST_BASIS,
+        base.CRT_TM,
+        base.PPN_TM,
+        base.AR_ID,
+        base.USER_CREATED,
+        base.IS_HDTG_DANANG,
+        base.BLOCKED_ACCOUNT
+FROM base
+JOIN tcimport.DIM_DEPOSIT cur
+    ON cur.DIMENSION_KEY = base.DIMENSION_KEY AND cur.EFF_TO_DATE IS NULL
+   AND md5(to_json(struct(cur.AC_MIDDLEMAN_LD, cur.DEPO_PROD_CODE, cur.DEPO_PROD_NAME, cur.START_DATE, cur.ACCOUNT_NO, cur.BRANCH_CODE, cur.CUSTOMER_ID, cur.ROLLOVER_DATE, cur.MATURITY_DATE, cur.ACCOUNT_OFFICER_ID, cur.FTP_TYPE_BOND, cur.ACCOUNT_STATUS, cur.FTP_RIGHT, cur.NEXT_RIGHTS_DATE, cur.FTP_TERM_RIGHT, cur.INTEREST_TYPE, cur.MATURITY_TREATMENT, cur.CUSTGROUP_AR, cur.INTEREST_BASIS, cur.AR_ID, cur.USER_CREATED, cur.IS_HDTG_DANANG, cur.BLOCKED_ACCOUNT))) &lt;&gt; md5(to_json(struct(base.AC_MIDDLEMAN_LD, base.DEPO_PROD_CODE, base.DEPO_PROD_NAME, base.START_DATE, base.ACCOUNT_NO, base.BRANCH_CODE, base.CUSTOMER_ID, base.ROLLOVER_DATE, base.MATURITY_DATE, base.ACCOUNT_OFFICER_ID, base.FTP_TYPE_BOND, base.ACCOUNT_STATUS, base.FTP_RIGHT, base.NEXT_RIGHTS_DATE, base.FTP_TERM_RIGHT, base.INTEREST_TYPE, base.MATURITY_TREATMENT, base.CUSTGROUP_AR, base.INTEREST_BASIS, base.AR_ID, base.USER_CREATED, base.IS_HDTG_DANANG, base.BLOCKED_ACCOUNT)))
+) staged
+ON tgt.DIMENSION_KEY = staged.mergeKey AND tgt.EFF_TO_DATE IS NULL
+WHEN MATCHED AND md5(to_json(struct(tgt.AC_MIDDLEMAN_LD, tgt.DEPO_PROD_CODE, tgt.DEPO_PROD_NAME, tgt.START_DATE, tgt.ACCOUNT_NO, tgt.BRANCH_CODE, tgt.CUSTOMER_ID, tgt.ROLLOVER_DATE, tgt.MATURITY_DATE, tgt.ACCOUNT_OFFICER_ID, tgt.FTP_TYPE_BOND, tgt.ACCOUNT_STATUS, tgt.FTP_RIGHT, tgt.NEXT_RIGHTS_DATE, tgt.FTP_TERM_RIGHT, tgt.INTEREST_TYPE, tgt.MATURITY_TREATMENT, tgt.CUSTGROUP_AR, tgt.INTEREST_BASIS, tgt.AR_ID, tgt.USER_CREATED, tgt.IS_HDTG_DANANG, tgt.BLOCKED_ACCOUNT))) &lt;&gt; md5(to_json(struct(staged.AC_MIDDLEMAN_LD, staged.DEPO_PROD_CODE, staged.DEPO_PROD_NAME, staged.START_DATE, staged.ACCOUNT_NO, staged.BRANCH_CODE, staged.CUSTOMER_ID, staged.ROLLOVER_DATE, staged.MATURITY_DATE, staged.ACCOUNT_OFFICER_ID, staged.FTP_TYPE_BOND, staged.ACCOUNT_STATUS, staged.FTP_RIGHT, staged.NEXT_RIGHTS_DATE, staged.FTP_TERM_RIGHT, staged.INTEREST_TYPE, staged.MATURITY_TREATMENT, staged.CUSTGROUP_AR, staged.INTEREST_BASIS, staged.AR_ID, staged.USER_CREATED, staged.IS_HDTG_DANANG, staged.BLOCKED_ACCOUNT)))
+    THEN UPDATE SET tgt.EFF_TO_DATE = date_sub(TO_DATE(:DATADT,'yyyyMMdd'),1)
+WHEN NOT MATCHED
+    THEN INSERT (
+        DIMENSION_KEY,
+        EFF_FROM_DATE,
+        EFF_TO_DATE,
+        AC_MIDDLEMAN_LD,
+        DEPO_PROD_CODE,
+        DEPO_PROD_NAME,
+        START_DATE,
+        ACCOUNT_NO,
+        BRANCH_CODE,
+        CUSTOMER_ID,
+        ROLLOVER_DATE,
+        MATURITY_DATE,
+        ACCOUNT_OFFICER_ID,
+        FTP_TYPE_BOND,
+        ACCOUNT_STATUS,
+        FTP_RIGHT,
+        NEXT_RIGHTS_DATE,
+        FTP_TERM_RIGHT,
+        INTEREST_TYPE,
+        MATURITY_TREATMENT,
+        CUSTGROUP_AR,
+        INTEREST_BASIS,
+        CRT_TM,
+        PPN_TM,
+        AR_ID,
+        USER_CREATED,
+        IS_HDTG_DANANG,
+        BLOCKED_ACCOUNT
+    ) VALUES (
+        staged.DIMENSION_KEY,
+        TO_DATE(:DATADT,'yyyyMMdd'),
+        CAST(NULL AS DATE),
+        staged.AC_MIDDLEMAN_LD,
+        staged.DEPO_PROD_CODE,
+        staged.DEPO_PROD_NAME,
+        staged.START_DATE,
+        staged.ACCOUNT_NO,
+        staged.BRANCH_CODE,
+        staged.CUSTOMER_ID,
+        staged.ROLLOVER_DATE,
+        staged.MATURITY_DATE,
+        staged.ACCOUNT_OFFICER_ID,
+        staged.FTP_TYPE_BOND,
+        staged.ACCOUNT_STATUS,
+        staged.FTP_RIGHT,
+        staged.NEXT_RIGHTS_DATE,
+        staged.FTP_TERM_RIGHT,
+        staged.INTEREST_TYPE,
+        staged.MATURITY_TREATMENT,
+        staged.CUSTGROUP_AR,
+        staged.INTEREST_BASIS,
+        staged.CRT_TM,
+        staged.PPN_TM,
+        staged.AR_ID,
+        staged.USER_CREATED,
+        staged.IS_HDTG_DANANG,
+        staged.BLOCKED_ACCOUNT
+    );
 </t>
   </si>
   <si>
@@ -1003,7 +1113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1076,11 +1186,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1158,7 +1263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1189,9 +1294,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1219,7 +1321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1532,17 +1634,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:7" ht="24">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1557,19 +1659,19 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1580,11 +1682,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1593,11 +1695,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1606,11 +1708,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1619,11 +1721,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1632,11 +1734,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1680,13 +1782,13 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="18"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1741,7 +1843,7 @@
       <c r="B3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1763,24 +1865,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="13" t="s">
@@ -1802,7 +1904,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24">
+    <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>38</v>
       </c>
@@ -2002,7 +2104,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>90</v>
       </c>
@@ -2102,7 +2204,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24">
+    <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="14" t="s">
         <v>115</v>
       </c>
@@ -2143,16 +2245,16 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-    </row>
-    <row r="24" spans="1:6" ht="38.25">
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+    </row>
+    <row r="24" spans="1:6" ht="38.25" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>126</v>
       </c>
@@ -2172,7 +2274,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="36">
+    <row r="25" spans="1:6" ht="36" customHeight="1">
       <c r="A25" s="14" t="s">
         <v>8</v>
       </c>
@@ -2192,7 +2294,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="36">
+    <row r="26" spans="1:6" ht="36" customHeight="1">
       <c r="A26" s="14" t="s">
         <v>8</v>
       </c>
@@ -2213,7 +2315,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="36">
+    <row r="27" spans="1:6" ht="36" customHeight="1">
       <c r="A27" s="14" t="s">
         <v>8</v>
       </c>
@@ -2233,7 +2335,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="36">
+    <row r="28" spans="1:6" ht="36" customHeight="1">
       <c r="A28" s="14" t="s">
         <v>8</v>
       </c>
@@ -2253,7 +2355,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="36">
+    <row r="29" spans="1:6" ht="36" customHeight="1">
       <c r="A29" s="14" t="s">
         <v>8</v>
       </c>
@@ -2273,7 +2375,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="36">
+    <row r="30" spans="1:6" ht="36" customHeight="1">
       <c r="A30" s="14" t="s">
         <v>8</v>
       </c>
@@ -2293,7 +2395,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="36">
+    <row r="31" spans="1:6" ht="36" customHeight="1">
       <c r="A31" s="14" t="s">
         <v>8</v>
       </c>
@@ -2313,7 +2415,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="36">
+    <row r="32" spans="1:6" ht="36" customHeight="1">
       <c r="A32" s="14" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2435,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="36">
+    <row r="33" spans="1:6" ht="36" customHeight="1">
       <c r="A33" s="14" t="s">
         <v>8</v>
       </c>
@@ -2353,7 +2455,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="36">
+    <row r="34" spans="1:6" ht="36" customHeight="1">
       <c r="A34" s="14" t="s">
         <v>8</v>
       </c>
@@ -2373,7 +2475,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="36">
+    <row r="35" spans="1:6" ht="36" customHeight="1">
       <c r="A35" s="14" t="s">
         <v>8</v>
       </c>
@@ -2393,7 +2495,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="36">
+    <row r="36" spans="1:6" ht="36" customHeight="1">
       <c r="A36" s="14" t="s">
         <v>8</v>
       </c>
@@ -2413,7 +2515,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="36">
+    <row r="37" spans="1:6" ht="36" customHeight="1">
       <c r="A37" s="14" t="s">
         <v>8</v>
       </c>
@@ -2433,7 +2535,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="36">
+    <row r="38" spans="1:6" ht="36" customHeight="1">
       <c r="A38" s="14" t="s">
         <v>8</v>
       </c>
@@ -2453,7 +2555,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="36">
+    <row r="39" spans="1:6" ht="36" customHeight="1">
       <c r="A39" s="14" t="s">
         <v>8</v>
       </c>
@@ -2473,7 +2575,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="36">
+    <row r="40" spans="1:6" ht="36" customHeight="1">
       <c r="A40" s="14" t="s">
         <v>8</v>
       </c>
@@ -2493,7 +2595,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="36">
+    <row r="41" spans="1:6" ht="36" customHeight="1">
       <c r="A41" s="14" t="s">
         <v>8</v>
       </c>
@@ -2513,7 +2615,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="36">
+    <row r="42" spans="1:6" ht="36" customHeight="1">
       <c r="A42" s="14" t="s">
         <v>8</v>
       </c>
@@ -2533,7 +2635,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="36">
+    <row r="43" spans="1:6" ht="36" customHeight="1">
       <c r="A43" s="14" t="s">
         <v>8</v>
       </c>
@@ -2553,7 +2655,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="36">
+    <row r="44" spans="1:6" ht="36" customHeight="1">
       <c r="A44" s="14" t="s">
         <v>8</v>
       </c>
@@ -2573,7 +2675,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="36">
+    <row r="45" spans="1:6" ht="36" customHeight="1">
       <c r="A45" s="14" t="s">
         <v>8</v>
       </c>
@@ -2593,7 +2695,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="36">
+    <row r="46" spans="1:6" ht="36" customHeight="1">
       <c r="A46" s="14" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2715,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="36">
+    <row r="47" spans="1:6" ht="36" customHeight="1">
       <c r="A47" s="14" t="s">
         <v>8</v>
       </c>
@@ -2633,7 +2735,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="36">
+    <row r="48" spans="1:6" ht="36" customHeight="1">
       <c r="A48" s="14" t="s">
         <v>8</v>
       </c>
@@ -2653,7 +2755,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="36">
+    <row r="49" spans="1:6" ht="36" customHeight="1">
       <c r="A49" s="14" t="s">
         <v>8</v>
       </c>
@@ -2673,7 +2775,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="36">
+    <row r="50" spans="1:6" ht="36" customHeight="1">
       <c r="A50" s="14" t="s">
         <v>8</v>
       </c>
@@ -2693,7 +2795,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="36">
+    <row r="51" spans="1:6" ht="36" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>8</v>
       </c>
@@ -2713,7 +2815,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="36">
+    <row r="52" spans="1:6" ht="36" customHeight="1">
       <c r="A52" s="14" t="s">
         <v>8</v>
       </c>
@@ -2744,25 +2846,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2934,14 +3017,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{747614A4-FA71-4B20-9C82-5F415C7C3907}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B65236A1-A7FF-44F7-A4E9-D9501F285EF7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C18FE9AD-96C1-4DBA-938C-8556C65B7430}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5077E093-9A78-4A78-B261-90D5D3EDBDC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF91F718-5FC0-49B6-ACA8-A2BE878624D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723E22A8-6F3C-4684-9795-30DD1522B955}"/>
 </file>